--- a/オーダー端末/テスト仕様書兼結果報告書（PG実践Ⅱ）.xlsx
+++ b/オーダー端末/テスト仕様書兼結果報告書（PG実践Ⅱ）.xlsx
@@ -1,37 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\oicsrv\教員個人\m-shimizu\Private\授業準備\2026年度\PG実践Ⅱ\教材\第1回\PG実践Ⅱ_第1回実践課題①-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shira\source\repos\OrderApp\オーダー端末\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CC8AC0-D005-4BD4-B7D1-25D58DD9F720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3952BBED-1F46-4FF9-BF91-85A4E9B445E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="24735" windowHeight="13980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="テスト仕様書兼結果報告書（○○）" sheetId="14" r:id="rId1"/>
+    <sheet name="テスト仕様書兼結果報告書（kaikei）" sheetId="14" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'テスト仕様書兼結果報告書（○○）'!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'テスト仕様書兼結果報告書（kaikei）'!$1:$10</definedName>
   </definedNames>
   <calcPr calcId="162913" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="48">
   <si>
     <t>テストケース</t>
     <phoneticPr fontId="2"/>
@@ -190,6 +187,123 @@
   </si>
   <si>
     <t>PG実践Ⅱ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>券売機システム</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Kaikei.xaml.cs</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Kaikei</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>新規作成</t>
+    <rPh sb="0" eb="4">
+      <t>シンキサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>渡邊</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>WPF</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1-3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5-3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>6-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>6-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>7-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>7-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>8-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>8-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>9-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>9-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>成功</t>
+    <rPh sb="0" eb="2">
+      <t>セイコウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -259,7 +373,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -429,21 +543,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -927,23 +1026,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -952,97 +1051,76 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1054,101 +1132,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1159,23 +1168,104 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1493,11 +1583,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE74E09-83A5-4C9E-A9F1-0F8020959B2A}">
   <dimension ref="A1:L32"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="16.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="72.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="85" style="1" customWidth="1"/>
     <col min="5" max="5" width="6.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.21875" style="1" customWidth="1"/>
@@ -1508,43 +1599,43 @@
     <col min="13" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:12" ht="23.25" thickBot="1" x14ac:dyDescent="0.85">
+      <c r="A1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="44"/>
-    </row>
-    <row r="2" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="45" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="69"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.4" thickBot="1" x14ac:dyDescent="0.85">
+      <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="49" t="s">
+      <c r="B2" s="71"/>
+      <c r="C2" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="50"/>
+      <c r="D2" s="73"/>
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="52" t="s">
+      <c r="G2" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
       <c r="K2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1552,147 +1643,163 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="47"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="7"/>
+    <row r="3" spans="1:12" ht="15.4" thickTop="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46206</v>
+      </c>
+      <c r="G3" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A4" s="47"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
       <c r="E4" s="9"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
       <c r="K4" s="11"/>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A5" s="47" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A5" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="51"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="37"/>
       <c r="E5" s="9"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A6" s="47"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A6" s="51"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
       <c r="K6" s="15"/>
       <c r="L6" s="16"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7" s="47" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A7" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="57" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="37"/>
+      <c r="E7" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="61"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A8" s="47"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="63"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A9" s="47" t="s">
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="59"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A8" s="51"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="61"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A9" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="63"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A10" s="66"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="1:12" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="70" t="s">
+      <c r="B9" s="52"/>
+      <c r="C9" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="37"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="61"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A10" s="64"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="63"/>
+    </row>
+    <row r="11" spans="1:12" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.85">
+      <c r="A11" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="73"/>
-    </row>
-    <row r="12" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="74" t="s">
+      <c r="B11" s="40"/>
+      <c r="C11" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="42"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.4" thickBot="1" x14ac:dyDescent="0.85">
+      <c r="A12" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="75"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="2" t="s">
         <v>0</v>
       </c>
@@ -1714,334 +1821,540 @@
       <c r="I12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="76" t="s">
+      <c r="J12" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="76"/>
-      <c r="L12" s="77"/>
-    </row>
-    <row r="13" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="K12" s="45"/>
+      <c r="L12" s="46"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.4" thickTop="1" x14ac:dyDescent="0.8">
       <c r="A13" s="18">
         <v>1</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="79"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A14" s="24">
+      <c r="B13" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="31"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I13" s="21"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="48"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A14" s="23"/>
+      <c r="B14" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="33"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="50"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A15" s="23"/>
+      <c r="B15" s="77" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="33"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I15" s="26"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="38"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A16" s="23">
         <v>2</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="80"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A15" s="24">
+      <c r="B16" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="33"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I16" s="26"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="38"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A17" s="23"/>
+      <c r="B17" s="77" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I17" s="26"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="38"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A18" s="23">
         <v>3</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="69"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16" s="24">
+      <c r="B18" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I18" s="26"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="38"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A19" s="23"/>
+      <c r="B19" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I19" s="26"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="38"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A20" s="23">
         <v>4</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="69"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A17" s="24">
+      <c r="B20" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I20" s="26"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="38"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A21" s="23"/>
+      <c r="B21" s="78" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I21" s="26"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="38"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A22" s="23">
         <v>5</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="69"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A18" s="24">
+      <c r="B22" s="77" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I22" s="26"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="38"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A23" s="23"/>
+      <c r="B23" s="77" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="25"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I23" s="26"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="38"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A24" s="23"/>
+      <c r="B24" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I24" s="26"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="38"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A25" s="23">
         <v>6</v>
       </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="69"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A19" s="24">
+      <c r="B25" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I25" s="26"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="38"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A26" s="23"/>
+      <c r="B26" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="25"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I26" s="26"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="38"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A27" s="23">
         <v>7</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="69"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A20" s="24">
+      <c r="B27" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I27" s="26"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="38"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A28" s="23"/>
+      <c r="B28" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="25"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I28" s="26"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="38"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A29" s="23">
         <v>8</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="69"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A21" s="24">
+      <c r="B29" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I29" s="26"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="38"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A30" s="23"/>
+      <c r="B30" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I30" s="26"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="38"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.8">
+      <c r="A31" s="23">
         <v>9</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="69"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A22" s="24">
-        <v>10</v>
-      </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="69"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A23" s="24">
-        <v>11</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="69"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A24" s="24">
-        <v>12</v>
-      </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="69"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A25" s="24">
-        <v>13</v>
-      </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
-      <c r="L25" s="69"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A26" s="24">
-        <v>14</v>
-      </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="69"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A27" s="24">
-        <v>15</v>
-      </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="51"/>
-      <c r="L27" s="69"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A28" s="24">
-        <v>16</v>
-      </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="51"/>
-      <c r="L28" s="69"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A29" s="24">
-        <v>17</v>
-      </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="69"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A30" s="24">
-        <v>18</v>
-      </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="69"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A31" s="24">
-        <v>19</v>
-      </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="69"/>
-    </row>
-    <row r="32" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="31">
-        <v>20</v>
-      </c>
-      <c r="B32" s="32"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="82"/>
+      <c r="B31" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I31" s="26"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="38"/>
+    </row>
+    <row r="32" spans="1:12" ht="15.4" thickBot="1" x14ac:dyDescent="0.85">
+      <c r="A32" s="27"/>
+      <c r="B32" s="79" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" s="20">
+        <v>46206</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="22">
+        <v>46206</v>
+      </c>
+      <c r="I32" s="30"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="C2:D4"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="F7:L10"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="J19:L19"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="J21:L21"/>
     <mergeCell ref="J22:L22"/>
@@ -2054,34 +2367,6 @@
     <mergeCell ref="J29:L29"/>
     <mergeCell ref="J30:L30"/>
     <mergeCell ref="J31:L31"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:E10"/>
-    <mergeCell ref="F7:L10"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="C2:D4"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="G4:J4"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
